--- a/internal_doc/05.测试设计/story/mysql连接器/MySQL用例列表.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/MySQL用例列表.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="mysql原生自动化用例" sheetId="2" r:id="rId2"/>
+    <sheet name="mysql补充测试用例" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
   <si>
     <t>基本功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -139,6 +139,30 @@
   </si>
   <si>
     <t>多列、多表查询；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>用例名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可对接sequoiadb执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注(原因)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testlink上用例编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否提交githup</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -499,6 +523,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="3" max="3" width="38.625" customWidth="1"/>
+    <col min="4" max="4" width="20.25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
@@ -639,9 +667,37 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="3" max="3" width="36.5" customWidth="1"/>
+    <col min="4" max="5" width="28.25" customWidth="1"/>
+    <col min="6" max="6" width="30.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -649,9 +705,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="18.625" customWidth="1"/>
+    <col min="2" max="2" width="20.25" customWidth="1"/>
+    <col min="3" max="3" width="22.375" customWidth="1"/>
+    <col min="4" max="4" width="24.5" customWidth="1"/>
+    <col min="5" max="5" width="28.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/internal_doc/05.测试设计/story/mysql连接器/MySQL用例列表.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/MySQL用例列表.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="mysql原生自动化用例" sheetId="2" r:id="rId2"/>
     <sheet name="mysql补充测试用例" sheetId="3" r:id="rId3"/>
+    <sheet name="未实现自动化用例" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>基本功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -163,6 +164,10 @@
   </si>
   <si>
     <t>是否提交githup</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testlink上用例编号/目录</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -736,4 +741,28 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="32.25" customWidth="1"/>
+    <col min="2" max="2" width="26.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/internal_doc/05.测试设计/story/mysql连接器/MySQL用例列表.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/MySQL用例列表.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="99">
   <si>
     <t>基本功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -143,10 +143,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>目录</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>用例名</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -163,11 +159,262 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>是否提交githup</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>testlink上用例编号/目录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>事务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发事务暂未实现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常暂未实现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支持默认分区表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>在基本功能中验证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本功能：
+seqDB-13161:外键索引查询；
+seqDB-13163:全文索引查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SequoiaDB暂时不支持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本功能：
+seqDB-13122~seqDB-13127</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>并发用例，暂未实现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>drop</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>目录（t/）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_create</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_datatype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_blob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bype_date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_datetime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_timestamps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_ranges</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_varchar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>null</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>truncate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multi_update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_math</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_str</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>order_by_all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select_all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>join</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group_by</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_transaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rollback</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alias</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13068、13070</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13069、13074</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13095、13096</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13087、13088、13089、13090</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13093、13094</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13160、13162、13165</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_group</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13104、13105、13106、13107、13111、13112</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否提交github</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create_tables</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13070、13071、13072</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_tinyint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_smallint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_mediumint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13075、13076</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13077、13078</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13079、13080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13081、13082</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction_ddl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction_dml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction_dql</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -228,10 +475,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -672,10 +922,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
     <col min="2" max="2" width="13.875" customWidth="1"/>
     <col min="3" max="3" width="36.5" customWidth="1"/>
     <col min="4" max="5" width="28.25" customWidth="1"/>
@@ -684,22 +934,398 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
         <v>31</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>32</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" t="s">
         <v>33</v>
       </c>
-      <c r="D1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" t="s">
-        <v>34</v>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="B3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>13091</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>14430</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>13092</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>13097</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>13103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>13102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>13120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="B19" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>13116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="B20" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>13115</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="B21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>13113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="B22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>13114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>13100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="B24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>13119</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>13117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>13305</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>13306</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>13130</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>13131</v>
       </c>
     </row>
   </sheetData>
@@ -710,10 +1336,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18.625" customWidth="1"/>
+    <col min="1" max="1" width="23.25" customWidth="1"/>
     <col min="2" max="2" width="20.25" customWidth="1"/>
     <col min="3" max="3" width="22.375" customWidth="1"/>
     <col min="4" max="4" width="24.5" customWidth="1"/>
@@ -722,19 +1348,116 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" t="s">
         <v>31</v>
       </c>
-      <c r="B1" t="s">
-        <v>32</v>
-      </c>
       <c r="C1" t="s">
-        <v>36</v>
+        <v>85</v>
       </c>
       <c r="D1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>13167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>13132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="B11" t="s">
+        <v>98</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>13166</v>
       </c>
     </row>
   </sheetData>
@@ -745,7 +1468,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="32.25" customWidth="1"/>
@@ -753,11 +1476,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
         <v>37</v>
       </c>
-      <c r="B1" t="s">
-        <v>34</v>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="40.5">
+      <c r="A5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="27">
+      <c r="A6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/internal_doc/05.测试设计/story/mysql连接器/MySQL用例列表.xlsx
+++ b/internal_doc/05.测试设计/story/mysql连接器/MySQL用例列表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="120">
   <si>
     <t>基本功能</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -143,19 +143,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>用例名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否可对接sequoiadb执行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>备注(原因)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>testlink上用例编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -214,207 +202,337 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>sequoiadb_create</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_datatype</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_blob</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bype_date</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_datetime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_timestamps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_ranges</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_varchar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>null</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>truncate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>multi_update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_index</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_query</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_math</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_str</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>order_by_all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>limit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select_all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>subquery_all</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>join</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>group_by</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sequoiadb_transaction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rollback</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>alias</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>func_group</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否提交github</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>create_tables</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_tinyint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_smallint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>type_mediumint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13079、13080</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction_ddl</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction_dql</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>目录（t/）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>sequoiadb_create</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_datatype</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_blob</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bype_date</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_datetime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_timestamps</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_ranges</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_varchar</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>null</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>truncate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>multi_update</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_index</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>key</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_query</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>func_math</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>func_str</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>func_time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>order_by_all</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>limit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>select_all</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>subquery_all</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>join</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>group_by</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sequoiadb_transaction</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>commit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>rollback</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>alias</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13068、13070</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13069、13074</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13095、13096</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13087、13088、13089、13090</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13093、13094</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13160、13162、13165</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>func_group</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13104、13105、13106、13107、13111、13112</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否提交github</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>create_tables</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13070、13071、13072</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_tinyint</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_smallint</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>type_mediumint</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13075、13076</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13077、13078</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13079、13080</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>13081、13082</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>transaction_ddl</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>transaction_dml</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>transaction_dql</t>
+    <t>用例名</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否可对接sequoiadb执行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>testlink上用例编号</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13068： 创建数据库
+13070： 关联普通表，数据操作基本功能验证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13069：删除数据库
+13074：删除表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>13095：插入/查询/更新/删除text类型的记录
+13096：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>插入/查询/更新/删除blob类型的记录</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13091：插入/查询/更新/删除date类型的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14430：插入/查询/更新/删除datetime类型的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13087：插入/查询/更新/删除float有符号类型的记录
+13088：插入/查询/更新/删除float无符号类型的记录
+13089：插入/查询/更新/删除double有符号类型的记录
+13090：插入/查询/更新/删除double无符号类型的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13160：主键索引查询
+13162：唯一索引查询
+13165：创建索引</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13120：指定表别名查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">13116：使用聚集函数执行查询
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13115：使用数值处理函数执行查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13113：使用文本处理函数执行查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13114：使用日期和时间处理函数执行查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13100：带order by子句更新/删除记录
+13118：排序查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13119：指定返回行数执行查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13117：分组查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13104：where子句单条件查询
+13105：where子句and操作符查询
+13106：where子句or操作符查询
+13107：where子句not操作符查询
+13111：指定列查询
+13112：计算列、拼接列、列别名查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13305：子查询基本功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13306：联接查询基本功能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13130：事务提交</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13131：事务回滚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13070：关联普通表，数据操作基本功能验证
+13071：关联分区表，数据操作基本功能验证
+13072：关联主子表，数据操作基本功能验证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13075：插入/查询/更新/删除tiny有符号类型的记录
+13076：插入/查询/更新/删除tiny无符号类型的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13077：插入/查询/更新/删除smallint有符号类型的记录
+13078：插入/查询/更新/删除smallint无符号类型的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13081：插入/查询/更新/删除mediumint有符号类型的记录
+13082：插入/查询/更新/删除mediumint无符号类型的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13166:事务中执行DQL语句</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13167：事务中执行DDL语句</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13092：插入/查询/更新/删除timestamp类型的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13093：插入/查询/更新/删除char类型的记
+13094：插入/查询/更新/删除varchar类型的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13097：:插入/查询/更新/删除包含null的记录</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13103：truncate操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>13102：多表更新/删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注(原因)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否注释用例内容</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -422,7 +540,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -454,6 +572,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -475,11 +601,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -922,230 +1051,237 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.125" customWidth="1"/>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
-    <col min="3" max="3" width="36.5" customWidth="1"/>
-    <col min="4" max="5" width="28.25" customWidth="1"/>
+    <col min="2" max="2" width="18.625" customWidth="1"/>
+    <col min="3" max="3" width="26.375" customWidth="1"/>
+    <col min="4" max="4" width="21.5" customWidth="1"/>
+    <col min="5" max="5" width="43.125" customWidth="1"/>
     <col min="6" max="6" width="30.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" ht="29.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="27">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="27">
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="27">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6" t="s">
         <v>48</v>
       </c>
-      <c r="B1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7" t="s">
         <v>49</v>
       </c>
-      <c r="B2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="B3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="108">
+      <c r="B8" t="s">
         <v>50</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="B9" t="s">
         <v>51</v>
       </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="B6" t="s">
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="27">
+      <c r="B10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="B11" t="s">
         <v>52</v>
       </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>13091</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>14430</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="B8" t="s">
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="B12" t="s">
         <v>54</v>
       </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="B9" t="s">
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="B13" t="s">
         <v>55</v>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>13092</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="B10" t="s">
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="40.5">
+      <c r="A16" t="s">
         <v>57</v>
       </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="B12" t="s">
+      <c r="B16" t="s">
         <v>58</v>
       </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>13097</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="B13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>13103</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="B14" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>13102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" t="s">
-        <v>62</v>
-      </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
-      <c r="E16" t="s">
-        <v>82</v>
+      <c r="E16" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1153,13 +1289,13 @@
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18">
-        <v>13120</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="27">
       <c r="B19" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -1167,13 +1303,13 @@
       <c r="D19">
         <v>1</v>
       </c>
-      <c r="E19">
-        <v>13116</v>
+      <c r="E19" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="B20" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1181,13 +1317,13 @@
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="E20">
-        <v>13115</v>
+      <c r="E20" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="B21" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1195,13 +1331,13 @@
       <c r="D21">
         <v>1</v>
       </c>
-      <c r="E21">
-        <v>13113</v>
+      <c r="E21" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="B22" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1209,13 +1345,13 @@
       <c r="D22">
         <v>1</v>
       </c>
-      <c r="E22">
-        <v>13114</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="E22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="27">
       <c r="B23" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1223,13 +1359,13 @@
       <c r="D23">
         <v>1</v>
       </c>
-      <c r="E23">
-        <v>13100</v>
+      <c r="E23" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="B24" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1237,13 +1373,13 @@
       <c r="D24">
         <v>1</v>
       </c>
-      <c r="E24">
-        <v>13119</v>
+      <c r="E24" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="B25" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1251,13 +1387,13 @@
       <c r="D25">
         <v>1</v>
       </c>
-      <c r="E25">
-        <v>13117</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="E25" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="81">
       <c r="B26" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1265,13 +1401,13 @@
       <c r="D26">
         <v>1</v>
       </c>
-      <c r="E26" t="s">
-        <v>84</v>
+      <c r="E26" s="3" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="B27" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1279,13 +1415,13 @@
       <c r="D27">
         <v>1</v>
       </c>
-      <c r="E27">
-        <v>13305</v>
+      <c r="E27" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="B28" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -1293,16 +1429,16 @@
       <c r="D28">
         <v>1</v>
       </c>
-      <c r="E28">
-        <v>13306</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="E28" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="17.25" customHeight="1">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -1310,13 +1446,13 @@
       <c r="D31">
         <v>1</v>
       </c>
-      <c r="E31">
-        <v>13130</v>
+      <c r="E31" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="B32" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -1324,8 +1460,8 @@
       <c r="D32">
         <v>1</v>
       </c>
-      <c r="E32">
-        <v>13131</v>
+      <c r="E32" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1336,128 +1472,117 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.25" customWidth="1"/>
     <col min="2" max="2" width="20.25" customWidth="1"/>
     <col min="3" max="3" width="22.375" customWidth="1"/>
-    <col min="4" max="4" width="24.5" customWidth="1"/>
+    <col min="4" max="4" width="41.875" customWidth="1"/>
     <col min="5" max="5" width="28.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:5" ht="35.25" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
+    </row>
+    <row r="2" spans="1:5" ht="40.5">
       <c r="A2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="D2" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="54">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="D4" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="54">
       <c r="B5" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
-      <c r="D5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="D5" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="54">
       <c r="B6" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6" t="s">
-        <v>95</v>
+      <c r="D6" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="B7" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
-      <c r="D9">
-        <v>13167</v>
+      <c r="D9" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="B10" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
-      <c r="D10">
-        <v>13132</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="B11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>13166</v>
+      <c r="D10" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1477,50 +1602,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="40.5">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="27">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
